--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2566" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2566" uniqueCount="485">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedTransferEncounter</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedTransferEncounter</t>
   </si>
   <si>
     <t>Version</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>MOPED Transfer Encounter</t>
+    <t>MOPED TransferEncounter</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,19 +60,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:21:37+00:00</t>
+    <t>2025-03-11T16:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ELGA</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>ELGA (https://www.elga.gv.at/)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -599,6 +599,14 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://elga.moped.at/CodeSystem/MopedEncounterTypesCS"/&gt;
+    &lt;code value="TENC"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>A specific code indicating type of service provided</t>
   </si>
   <si>
@@ -686,7 +694,7 @@
     <t>Different use-cases are likely to have different permitted transitions between states, such as an Emergency department could use `arrived` when the patient first presents, then `triaged` once has been assessed by a nurse, then `receiving-care` once treatment begins, however other sectors may use a different set of these values, or their own custom set in place of this example valueset provided.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-Anwesenheitsart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/Anwesenheitsart</t>
   </si>
   <si>
     <t>Encounter.episodeOfCare</t>
@@ -747,7 +755,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedEncounter)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedEncounter)
 </t>
   </si>
   <si>
@@ -771,7 +779,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedOrganizationAbteilung)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedOrganizationAbteilung)
 </t>
   </si>
   <si>
@@ -1345,7 +1353,7 @@
     <t>Altersgruppe</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-altersgruppe}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-altersgruppe}
 </t>
   </si>
   <si>
@@ -1450,7 +1458,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-abgangsart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/Abgangsart</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1896,7 +1904,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="74.65625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.48046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.25390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3556,7 +3564,7 @@
         <v>20</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>20</v>
@@ -3574,10 +3582,10 @@
         <v>178</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3610,24 +3618,24 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3650,13 +3658,13 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3686,10 +3694,10 @@
         <v>178</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3707,7 +3715,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3722,28 +3730,28 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3762,16 +3770,16 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3821,7 +3829,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3836,24 +3844,24 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3879,13 +3887,13 @@
         <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3915,7 +3923,7 @@
       </c>
       <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3933,7 +3941,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3962,10 +3970,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3988,13 +3996,13 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4045,7 +4053,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4063,25 +4071,25 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4100,13 +4108,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4157,7 +4165,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4172,13 +4180,13 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>20</v>
@@ -4186,10 +4194,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4212,13 +4220,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4269,7 +4277,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4290,7 +4298,7 @@
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
@@ -4298,10 +4306,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4309,7 +4317,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
@@ -4324,16 +4332,16 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4383,7 +4391,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4398,13 +4406,13 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -4412,10 +4420,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4438,13 +4446,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4495,7 +4503,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4510,24 +4518,24 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4550,16 +4558,16 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4609,7 +4617,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4621,27 +4629,27 @@
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4664,13 +4672,13 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4721,7 +4729,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4730,7 +4738,7 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>20</v>
@@ -4742,7 +4750,7 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
@@ -4750,10 +4758,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4782,7 +4790,7 @@
         <v>137</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>139</v>
@@ -4835,7 +4843,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4856,7 +4864,7 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4864,14 +4872,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4893,10 +4901,10 @@
         <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>139</v>
@@ -4951,7 +4959,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4980,10 +4988,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5009,13 +5017,13 @@
         <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5041,13 +5049,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5065,7 +5073,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5074,30 +5082,30 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5120,13 +5128,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5177,7 +5185,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5198,18 +5206,18 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5232,16 +5240,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5291,7 +5299,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5300,30 +5308,30 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5346,13 +5354,13 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5403,7 +5411,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5418,24 +5426,24 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5458,16 +5466,16 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5517,7 +5525,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5546,10 +5554,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5572,16 +5580,16 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5631,7 +5639,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5646,24 +5654,24 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5686,13 +5694,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5743,7 +5751,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5767,15 +5775,15 @@
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5798,13 +5806,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5855,7 +5863,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5879,15 +5887,15 @@
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5910,16 +5918,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5969,7 +5977,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5984,24 +5992,24 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6024,16 +6032,16 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6083,7 +6091,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6112,10 +6120,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6138,13 +6146,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6195,7 +6203,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6204,7 +6212,7 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>20</v>
@@ -6216,7 +6224,7 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6224,10 +6232,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6256,7 +6264,7 @@
         <v>137</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>139</v>
@@ -6309,7 +6317,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6330,7 +6338,7 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6338,14 +6346,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6367,10 +6375,10 @@
         <v>136</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>139</v>
@@ -6425,7 +6433,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6454,10 +6462,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6483,10 +6491,10 @@
         <v>166</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6517,7 +6525,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6535,7 +6543,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6564,14 +6572,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6590,13 +6598,13 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6626,10 +6634,10 @@
         <v>169</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6647,7 +6655,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6662,24 +6670,24 @@
         <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6702,16 +6710,16 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6761,7 +6769,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6782,7 +6790,7 @@
         <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6790,10 +6798,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6816,13 +6824,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6873,7 +6881,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6882,7 +6890,7 @@
         <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>20</v>
@@ -6894,7 +6902,7 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6902,10 +6910,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6934,7 +6942,7 @@
         <v>137</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>139</v>
@@ -6987,7 +6995,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7008,7 +7016,7 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -7016,14 +7024,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7045,10 +7053,10 @@
         <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>139</v>
@@ -7103,7 +7111,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7132,14 +7140,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7158,13 +7166,13 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7195,7 +7203,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7213,7 +7221,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7228,24 +7236,24 @@
         <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7271,10 +7279,10 @@
         <v>166</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7304,10 +7312,10 @@
         <v>169</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7325,7 +7333,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7346,18 +7354,18 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7380,16 +7388,16 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7439,7 +7447,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7460,7 +7468,7 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -7468,10 +7476,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7497,16 +7505,16 @@
         <v>166</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7534,10 +7542,10 @@
         <v>178</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7555,7 +7563,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7576,18 +7584,18 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7613,10 +7621,10 @@
         <v>166</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7646,10 +7654,10 @@
         <v>169</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7667,7 +7675,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7688,18 +7696,18 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7725,13 +7733,13 @@
         <v>166</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7760,10 +7768,10 @@
         <v>169</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -7781,7 +7789,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7802,18 +7810,18 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7836,16 +7844,16 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7895,7 +7903,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7916,7 +7924,7 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>20</v>
@@ -7924,10 +7932,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7950,13 +7958,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8007,7 +8015,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8016,7 +8024,7 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>20</v>
@@ -8028,7 +8036,7 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>20</v>
@@ -8036,10 +8044,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8065,10 +8073,10 @@
         <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8107,17 +8115,17 @@
         <v>20</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AC55" s="2"/>
       <c r="AD55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8146,13 +8154,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>20</v>
@@ -8174,13 +8182,13 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="L56" t="s" s="2">
-        <v>415</v>
-      </c>
       <c r="M56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8231,7 +8239,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8243,7 +8251,7 @@
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8260,14 +8268,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8289,10 +8297,10 @@
         <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>139</v>
@@ -8347,7 +8355,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8376,10 +8384,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8405,10 +8413,10 @@
         <v>148</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8459,7 +8467,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8483,15 +8491,15 @@
         <v>153</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8514,13 +8522,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8571,7 +8579,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8592,7 +8600,7 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>20</v>
@@ -8600,10 +8608,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8629,10 +8637,10 @@
         <v>166</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8662,10 +8670,10 @@
         <v>169</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -8683,7 +8691,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8704,18 +8712,18 @@
         <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8741,10 +8749,10 @@
         <v>166</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8774,10 +8782,10 @@
         <v>178</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -8795,7 +8803,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8816,18 +8824,18 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8850,13 +8858,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8907,7 +8915,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8928,18 +8936,18 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8965,10 +8973,10 @@
         <v>166</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8999,7 +9007,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9017,7 +9025,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9038,18 +9046,18 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9072,16 +9080,16 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9131,7 +9139,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9152,7 +9160,7 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>20</v>
@@ -9160,10 +9168,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9186,13 +9194,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9243,7 +9251,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9252,7 +9260,7 @@
         <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>20</v>
@@ -9264,7 +9272,7 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>20</v>
@@ -9272,10 +9280,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9304,7 +9312,7 @@
         <v>137</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>139</v>
@@ -9357,7 +9365,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9378,7 +9386,7 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>20</v>
@@ -9386,14 +9394,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9415,10 +9423,10 @@
         <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>139</v>
@@ -9473,7 +9481,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9502,10 +9510,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9528,13 +9536,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9585,7 +9593,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>88</v>
@@ -9600,24 +9608,24 @@
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9643,13 +9651,13 @@
         <v>108</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9678,10 +9686,10 @@
         <v>112</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9699,7 +9707,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9720,7 +9728,7 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>20</v>
@@ -9728,10 +9736,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9757,13 +9765,13 @@
         <v>166</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9792,10 +9800,10 @@
         <v>178</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -9813,7 +9821,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9842,10 +9850,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9868,13 +9876,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9925,7 +9933,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9946,7 +9954,7 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>20</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T10:11:40+00:00</t>
+    <t>2026-01-26T07:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:03:23+00:00</t>
+    <t>2026-01-26T07:12:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:12:25+00:00</t>
+    <t>2026-01-26T07:23:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T07:23:42+00:00</t>
+    <t>2026-03-01T19:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:57:07+00:00</t>
+    <t>2026-03-10T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T09:54:59+00:00</t>
+    <t>2026-03-12T09:42:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T09:42:23+00:00</t>
+    <t>2026-03-15T19:53:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T19:53:47+00:00</t>
+    <t>2026-03-24T19:35:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T19:35:33+00:00</t>
+    <t>2026-03-24T20:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T20:07:54+00:00</t>
+    <t>2026-03-29T08:30:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T08:30:46+00:00</t>
+    <t>2026-03-29T16:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T16:14:43+00:00</t>
+    <t>2026-04-07T06:39:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T06:39:12+00:00</t>
+    <t>2026-04-07T10:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:38:55+00:00</t>
+    <t>2026-04-07T11:10:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T11:10:24+00:00</t>
+    <t>2026-04-07T12:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T12:18:59+00:00</t>
+    <t>2026-04-07T19:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:20:35+00:00</t>
+    <t>2026-04-07T19:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T19:34:12+00:00</t>
+    <t>2026-04-08T06:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T06:34:39+00:00</t>
+    <t>2026-04-08T08:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T08:16:43+00:00</t>
+    <t>2026-04-17T10:34:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:34:11+00:00</t>
+    <t>2026-04-23T07:59:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T07:59:48+00:00</t>
+    <t>2026-04-29T07:12:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:12:28+00:00</t>
+    <t>2026-04-29T07:28:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T07:28:34+00:00</t>
+    <t>2026-04-29T09:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -582,7 +582,7 @@
     <t>MopedServiceType</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableReference(https://elga.moped.at/StructureDefinition/MopedKHOrganisationseinheit)
+    <t xml:space="preserve">CodeableReference(https://elga.moped.at/StructureDefinition/MopedKAOrganisationseinheit)
 </t>
   </si>
   <si>
@@ -925,7 +925,7 @@
     <t>Encounter.participant:FachlichZustaendigeOrganisationseinheit.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedKHOrganisationseinheit)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedKAOrganisationseinheit)
 </t>
   </si>
   <si>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T09:14:27+00:00</t>
+    <t>2026-05-05T07:22:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T07:22:12+00:00</t>
+    <t>2026-05-15T07:39:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T07:39:15+00:00</t>
+    <t>2026-05-15T09:26:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -674,7 +674,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedPatient)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedBasisPatientvbPK|https://elga.moped.at/StructureDefinition/MopedBasisPatientKlarname)
 </t>
   </si>
   <si>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MopedTransferEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T09:26:31+00:00</t>
+    <t>2026-05-22T08:08:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
